--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_113_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_113_R12.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6471</v>
+        <v>1.2861</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1956</v>
+        <v>2.9093</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5485</v>
+        <v>-1.6232</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4014</v>
+        <v>-2.1605</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0311</v>
+        <v>-0.4709</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4325</v>
+        <v>-1.6896</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9801</v>
+        <v>0.7776</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7547</v>
+        <v>0.9382</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2254</v>
+        <v>-0.1607</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5787</v>
+        <v>-2.9381</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.7858</v>
+        <v>-1.4091</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7929</v>
+        <v>-1.529</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7543</v>
+        <v>-0.002</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6247</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1296</v>
+        <v>-0.0769</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.42</v>
+        <v>0.9406</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2449</v>
+        <v>3.3883</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8249</v>
+        <v>-2.4477</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1605</v>
+        <v>1.4014</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4709</v>
+        <v>-1.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6896</v>
+        <v>2.4325</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7776</v>
+        <v>4.9801</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9382</v>
+        <v>1.7547</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1607</v>
+        <v>3.2254</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9381</v>
+        <v>-3.5787</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4091</v>
+        <v>-2.7858</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.529</v>
+        <v>-0.7929</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8681</v>
+        <v>-0.4608</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5895</v>
+        <v>-0.4321</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2785</v>
+        <v>-0.0288</v>
       </c>
       <c r="V3" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. TOTE</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4452</v>
+        <v>-0.9866</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1609</v>
+        <v>-1.3597</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6061</v>
+        <v>0.373</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5233</v>
+        <v>-0.5906</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5942</v>
+        <v>0.3697</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1175</v>
+        <v>-0.9603</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8144</v>
+        <v>-0.2118</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6672</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3377</v>
+        <v>-0.3788</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.073</v>
+        <v>-0.168</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2647</v>
+        <v>-0.2108</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8461</v>
+        <v>0.0679</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9006</v>
+        <v>0.0119</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0545</v>
+        <v>0.056</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>L. TOTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2562</v>
+        <v>-1.1694</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5956</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3394</v>
+        <v>-1.7405</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5906</v>
+        <v>-0.5233</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3697</v>
+        <v>0.5942</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9603</v>
+        <v>-1.1175</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2118</v>
+        <v>1.8144</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.6672</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.1472</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3788</v>
+        <v>-2.3377</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.168</v>
+        <v>-1.073</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2108</v>
+        <v>-1.2647</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2016</v>
+        <v>0.1219</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.224</v>
+        <v>0.3108</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0224</v>
+        <v>-0.1889</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7794</v>
+        <v>-1.6779</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8394</v>
+        <v>-0.9739</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4628</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0597</v>
+        <v>0.1612</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2838</v>
+        <v>0.1494</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8397</v>
+        <v>-1.8226</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9468</v>
+        <v>-0.8288</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.893</v>
+        <v>-0.9938</v>
       </c>
       <c r="G7" t="n">
         <v>-4.3554</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9871</v>
+        <v>-0.97</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1123</v>
+        <v>-0.9944</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1252</v>
+        <v>0.0244</v>
       </c>
       <c r="V7" t="n">
         <v>4.4306</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8869</v>
+        <v>-2.317</v>
       </c>
       <c r="E8" t="n">
-        <v>1.038</v>
+        <v>0.8768</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9249</v>
+        <v>-3.1938</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3576</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1511</v>
+        <v>-0.279</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4753</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6264</v>
+        <v>0.3576</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.127</v>
+        <v>-2.6831</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3207</v>
+        <v>-0.9105</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8062</v>
+        <v>-1.7726</v>
       </c>
       <c r="G9" t="n">
         <v>-3.959</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5125</v>
+        <v>0.9564</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2151</v>
+        <v>0.6253</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2974</v>
+        <v>0.331</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0631</v>
+        <v>-3.0049</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8166</v>
+        <v>-0.624</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2465</v>
+        <v>-2.3809</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3731</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1502</v>
+        <v>0.2084</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1687</v>
+        <v>0.0239</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3189</v>
+        <v>0.1845</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7122</v>
+        <v>-4.7129</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8563</v>
+        <v>-2.0922</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.856</v>
+        <v>-2.6207</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6846</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4194</v>
+        <v>-1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.55</v>
+        <v>-0.7859</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8694</v>
+        <v>-0.6341</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.725</v>
+        <v>-6.2464</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4329</v>
+        <v>-3.1223</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2921</v>
+        <v>-3.1241</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3998</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3974</v>
+        <v>-0.9188</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1123</v>
+        <v>-0.8017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.7676</v>
+        <v>-22.3941</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2695</v>
+        <v>-1.8961</v>
       </c>
       <c r="F13" t="n">
         <v>-20.4982</v>
@@ -1468,13 +1468,13 @@
         <v>11.5977</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.9083</v>
+        <v>-2.5348</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.965100000000001</v>
+        <v>-2.592</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05700000000000005</v>
+        <v>0.05710000000000003</v>
       </c>
       <c r="V13" t="n">
         <v>2.2862</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8297</v>
+        <v>6.3998</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1068</v>
+        <v>5.7192</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7228</v>
+        <v>0.6806</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1587</v>
+        <v>4.8886</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8302</v>
+        <v>1.7334</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3285</v>
+        <v>3.1552</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3477</v>
+        <v>5.2823</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2741</v>
+        <v>2.8064</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0736</v>
+        <v>2.4759</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.3937</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4439</v>
+        <v>-1.073</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2549</v>
+        <v>0.6793</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1546,28 +1546,28 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6709</v>
+        <v>0.5808</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9189</v>
+        <v>-0.0116</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7521</v>
+        <v>0.5924</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0795</v>
+        <v>5.7567</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3653</v>
+        <v>2.8094</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7141999999999999</v>
+        <v>2.9473</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8886</v>
+        <v>4.1587</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7334</v>
+        <v>2.8302</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1552</v>
+        <v>1.3285</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2823</v>
+        <v>3.3477</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8064</v>
+        <v>3.2741</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4759</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3937</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.073</v>
+        <v>-0.4439</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6793</v>
+        <v>1.2549</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1624,22 +1624,22 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2605</v>
+        <v>1.598</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3655</v>
+        <v>0.6214</v>
       </c>
       <c r="U15" t="n">
-        <v>0.626</v>
+        <v>0.9766</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.413</v>
+        <v>5.4174</v>
       </c>
       <c r="E16" t="n">
-        <v>7.0038</v>
+        <v>6.414</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5908</v>
+        <v>-0.9967</v>
       </c>
       <c r="G16" t="n">
         <v>4.2449</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4722</v>
+        <v>0.4766</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0499</v>
+        <v>0.4602</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5777</v>
+        <v>0.0165</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8272</v>
+        <v>4.4233</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0621</v>
+        <v>2.7698</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7651</v>
+        <v>1.6535</v>
       </c>
       <c r="G17" t="n">
         <v>3.995</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.76</v>
+        <v>1.3561</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5895</v>
+        <v>0.1182</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3495</v>
+        <v>1.238</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5926</v>
+        <v>2.4082</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5084</v>
+        <v>1.5994</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9158</v>
+        <v>0.8087</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1519</v>
+        <v>3.5972</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5426</v>
+        <v>1.1681</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6094</v>
+        <v>2.4291</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8709</v>
+        <v>3.9303</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1545</v>
+        <v>1.9697</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7164</v>
+        <v>1.9606</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.719</v>
+        <v>-0.333</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.612</v>
+        <v>-0.8016</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.107</v>
+        <v>0.4685</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4406</v>
+        <v>0.2928</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1889</v>
+        <v>-0.1531</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2517</v>
+        <v>0.4459</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4132</v>
+        <v>2.2787</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7174</v>
+        <v>4.2725</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6958</v>
+        <v>-1.9938</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5972</v>
+        <v>3.1519</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1681</v>
+        <v>1.5426</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4291</v>
+        <v>1.6094</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9303</v>
+        <v>3.8709</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9697</v>
+        <v>2.1545</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9606</v>
+        <v>1.7164</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.333</v>
+        <v>-0.719</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8016</v>
+        <v>-0.612</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4685</v>
+        <v>-0.107</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2978</v>
+        <v>0.1267</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0351</v>
+        <v>-0.047</v>
       </c>
       <c r="U19" t="n">
-        <v>0.333</v>
+        <v>0.1737</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0433</v>
+        <v>1.16</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7663</v>
+        <v>-0.1765</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8096</v>
+        <v>1.3365</v>
       </c>
       <c r="G20" t="n">
         <v>1.101</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4494</v>
+        <v>0.6673</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0655</v>
+        <v>0.5924</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0192</v>
+        <v>-0.0588</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1704</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1896</v>
+        <v>0.1116</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0322</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0514</v>
+        <v>-0.0266</v>
       </c>
       <c r="T21" t="n">
         <v>-0.224</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2754</v>
+        <v>0.1975</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5404</v>
+        <v>-0.2823</v>
       </c>
       <c r="E22" t="n">
         <v>-0.2072</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3332</v>
+        <v>-0.0751</v>
       </c>
       <c r="G22" t="n">
         <v>0.4671</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4714</v>
+        <v>-0.2133</v>
       </c>
       <c r="T22" t="n">
         <v>-0.224</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2473</v>
+        <v>0.0108</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7783</v>
+        <v>-0.4409</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5723</v>
+        <v>1.0441</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3506</v>
+        <v>-1.4851</v>
       </c>
       <c r="G23" t="n">
         <v>0.423</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1291</v>
+        <v>0.2082</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5895</v>
+        <v>-0.1177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4604</v>
+        <v>0.326</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8014</v>
+        <v>-0.5434</v>
       </c>
       <c r="E24" t="n">
         <v>-1.0683</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2668</v>
+        <v>0.5249</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4873</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5461</v>
+        <v>-0.288</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2473</v>
+        <v>0.0108</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3297</v>
+        <v>-2.1782</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6257</v>
+        <v>-2.5078</v>
       </c>
       <c r="F25" t="n">
-        <v>0.296</v>
+        <v>0.3296</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0427</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4494</v>
+        <v>-0.2978</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1418</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>22.7679</v>
+        <v>24.3405</v>
       </c>
       <c r="E26" t="n">
         <v>20.4982</v>
       </c>
       <c r="F26" t="n">
-        <v>2.269499999999999</v>
+        <v>3.842</v>
       </c>
       <c r="G26" t="n">
         <v>24.4652</v>
@@ -2482,13 +2482,13 @@
         <v>9.2784</v>
       </c>
       <c r="S26" t="n">
-        <v>2.907999999999999</v>
+        <v>4.480799999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.05689999999999973</v>
+        <v>-0.05690000000000006</v>
       </c>
       <c r="U26" t="n">
-        <v>2.9653</v>
+        <v>4.5382</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2862</v>
